--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487503_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487503_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.472</v>
+        <v>6.192</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2769</v>
+        <v>4.9434</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1951</v>
+        <v>1.2485</v>
       </c>
       <c r="G2" t="n">
         <v>4.9242</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9731</v>
+        <v>0.6931</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1733</v>
+        <v>0.8399</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2002</v>
+        <v>-0.1467</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2088</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5127</v>
+        <v>3.2862</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9807</v>
+        <v>1.6473</v>
       </c>
       <c r="F3" t="n">
-        <v>1.532</v>
+        <v>1.6389</v>
       </c>
       <c r="G3" t="n">
         <v>3.7514</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5577</v>
+        <v>0.3311</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0545</v>
+        <v>0.721</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4968</v>
+        <v>-0.3899</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2088</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2904</v>
+        <v>2.7162</v>
       </c>
       <c r="E4" t="n">
-        <v>1.847</v>
+        <v>2.3933</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4434</v>
+        <v>0.3229</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6678</v>
+        <v>0.4469</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.505</v>
+        <v>0.6897</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1728</v>
+        <v>-0.2429</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7355</v>
+        <v>0.6438</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5783</v>
+        <v>0.7554</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1572</v>
+        <v>-0.1116</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0677</v>
+        <v>-0.1969</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0833</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0156</v>
+        <v>-0.1313</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9585</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1128</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0214</v>
+        <v>0.1898</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8475</v>
+        <v>0.2576</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1739</v>
+        <v>-0.0678</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5597</v>
+        <v>1.492</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3768</v>
+        <v>1.492</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8497</v>
+        <v>1.5138</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6605</v>
+        <v>0.744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1892</v>
+        <v>0.7698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4469</v>
+        <v>0.8054</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6897</v>
+        <v>0.3556</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2429</v>
+        <v>0.4498</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6438</v>
+        <v>1.1428</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7554</v>
+        <v>1.1024</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1116</v>
+        <v>0.0404</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1969</v>
+        <v>-0.3375</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.7468</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1313</v>
+        <v>0.4093</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6767</v>
+        <v>-0.1337</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4752</v>
+        <v>-0.0659</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2014</v>
+        <v>-0.0678</v>
       </c>
       <c r="V5" t="n">
-        <v>1.492</v>
+        <v>-0.3329</v>
       </c>
       <c r="W5" t="n">
-        <v>1.492</v>
+        <v>-0.3329</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0778</v>
+        <v>1.4625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3347</v>
+        <v>1.2329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7431</v>
+        <v>0.2296</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8054</v>
+        <v>2.6678</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3556</v>
+        <v>-0.505</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4498</v>
+        <v>3.1728</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1428</v>
+        <v>3.7355</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1024</v>
+        <v>0.5783</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>3.1572</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3375</v>
+        <v>-1.0677</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7468</v>
+        <v>-1.0833</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4093</v>
+        <v>0.0156</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1751</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.1128</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5697</v>
+        <v>0.1935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>0.2335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0945</v>
+        <v>-0.04</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3329</v>
+        <v>0.5597</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3329</v>
+        <v>1.3768</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8171</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7723</v>
+        <v>0.7189</v>
       </c>
       <c r="E7" t="n">
         <v>0.5141</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2583</v>
+        <v>0.2048</v>
       </c>
       <c r="G7" t="n">
         <v>0.7068</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1303</v>
+        <v>-0.1838</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0115</v>
+        <v>-0.065</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1941</v>
+        <v>0.5011</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3866</v>
+        <v>-1.0796</v>
       </c>
       <c r="F8" t="n">
         <v>1.5807</v>
@@ -1078,10 +1078,10 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7528</v>
+        <v>-0.4458</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3388</v>
+        <v>-0.0318</v>
       </c>
       <c r="U8" t="n">
         <v>-0.414</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6574</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7992</v>
+        <v>-1.2675</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1418</v>
+        <v>1.3389</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4794</v>
+        <v>-1.8746</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1977</v>
+        <v>-0.505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.677</v>
+        <v>-1.3697</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.621</v>
+        <v>-0.6778</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0612</v>
+        <v>0.7127</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>-1.3904</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1416</v>
+        <v>-1.1969</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1364</v>
+        <v>-1.2176</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0052</v>
+        <v>0.0208</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>3.5253</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3739</v>
+        <v>-0.0618</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>-0.1647</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1957</v>
+        <v>0.1029</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6161</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0924</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0489</v>
+        <v>0.1558</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.733</v>
+        <v>-0.6795</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7581</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4155</v>
+        <v>-0.1573</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1012</v>
+        <v>0.1035</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3143</v>
+        <v>-0.2608</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9163</v>
+        <v>-0.5712</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.469</v>
+        <v>-0.7398</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5528</v>
+        <v>0.1685</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8746</v>
+        <v>-0.4794</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.505</v>
+        <v>0.1977</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3697</v>
+        <v>-0.677</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6778</v>
+        <v>-0.621</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7127</v>
+        <v>0.0612</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3904</v>
+        <v>-0.6822</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1969</v>
+        <v>0.1416</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2176</v>
+        <v>0.1364</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0208</v>
+        <v>0.0052</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5253</v>
+        <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0495</v>
+        <v>-0.2877</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3662</v>
+        <v>-0.1188</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3168</v>
+        <v>-0.1689</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6161</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.404</v>
+        <v>-1.7807</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.022</v>
+        <v>-1.3719</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.382</v>
+        <v>-0.4088</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1872</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3915</v>
+        <v>0.0149</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3258</v>
+        <v>-0.0241</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5934</v>
+        <v>-3.8793</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6783</v>
+        <v>-1.0711</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9151</v>
+        <v>-2.8082</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3828</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8482</v>
+        <v>0.5623</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0081</v>
+        <v>0.6152</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1599</v>
+        <v>-0.0529</v>
       </c>
       <c r="V13" t="n">
         <v>-1.492</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.816100000000002</v>
+        <v>9.707300000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>5.209900000000001</v>
+        <v>6.100899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6063</v>
+        <v>3.6061</v>
       </c>
       <c r="G14" t="n">
-        <v>7.129799999999996</v>
+        <v>7.129799999999998</v>
       </c>
       <c r="H14" t="n">
         <v>9.884499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.754900000000001</v>
+        <v>-2.7549</v>
       </c>
       <c r="J14" t="n">
         <v>13.7651</v>
@@ -1546,10 +1546,10 @@
         <v>17.6262</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1765</v>
+        <v>0.7146000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3556</v>
+        <v>2.2466</v>
       </c>
       <c r="U14" t="n">
         <v>-1.5319</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9267</v>
+        <v>3.4535</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7112</v>
+        <v>3.5855</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2155</v>
+        <v>-0.132</v>
       </c>
       <c r="G15" t="n">
         <v>2.3904</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9821</v>
+        <v>0.5089</v>
       </c>
       <c r="T15" t="n">
-        <v>1.618</v>
+        <v>0.4923</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3641</v>
+        <v>0.0166</v>
       </c>
       <c r="V15" t="n">
         <v>2.7086</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1399</v>
+        <v>0.6997</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9578</v>
+        <v>1.1147</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.4151</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1207</v>
+        <v>-3.8943</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6962</v>
+        <v>-4.8694</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4245</v>
+        <v>0.9752</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7895</v>
+        <v>-1.2704</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1024</v>
+        <v>-1.8103</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6871</v>
+        <v>0.5399</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6687</v>
+        <v>-2.6238</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4062</v>
+        <v>-3.0591</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2625</v>
+        <v>0.4353</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9792</v>
+        <v>2.7419</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8244</v>
+        <v>-0.3058</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1269</v>
+        <v>-0.2658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3024</v>
+        <v>-0.04</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8260999999999999</v>
+        <v>2.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.651</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.4931</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SANCHEZ PARRES</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1776</v>
+        <v>-0.1773</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.3018</v>
+        <v>0.3438</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1242</v>
+        <v>-0.5211</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3614</v>
+        <v>1.1207</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1545</v>
+        <v>0.6962</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7931</v>
+        <v>0.4245</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8937</v>
+        <v>1.7895</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.863</v>
+        <v>1.1024</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0308</v>
+        <v>0.6871</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4677</v>
+        <v>-0.6687</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2916</v>
+        <v>-0.4062</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8239</v>
+        <v>-0.2625</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4005</v>
+        <v>0.5073</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5505</v>
+        <v>0.5129</v>
       </c>
       <c r="U17" t="n">
-        <v>0.85</v>
+        <v>-0.0056</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>R. SANCHEZ PARRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2168</v>
+        <v>-0.7076</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0914</v>
+        <v>-3.4041</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3082</v>
+        <v>2.6965</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8943</v>
+        <v>-2.3614</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.8694</v>
+        <v>-3.1545</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9752</v>
+        <v>0.7931</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2704</v>
+        <v>-1.8937</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8103</v>
+        <v>-1.863</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5399</v>
+        <v>-0.0308</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6238</v>
+        <v>-0.4677</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.0591</v>
+        <v>-1.2916</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4353</v>
+        <v>0.8239</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7419</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
         <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2223</v>
+        <v>0.8704</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2892</v>
+        <v>0.4482</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0669</v>
+        <v>0.4223</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1578</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.651</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8847</v>
+        <v>-1.1973</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3153</v>
+        <v>1.599</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2</v>
+        <v>-2.7963</v>
       </c>
       <c r="G19" t="n">
         <v>0.9883999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1476</v>
+        <v>-0.165</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0545</v>
+        <v>0.3382</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9069</v>
+        <v>-0.5031</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8249</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>J. BUENO DE LA ROSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3174</v>
+        <v>-1.3023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7008</v>
+        <v>-1.095</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6166</v>
+        <v>-0.2073</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8632</v>
+        <v>-1.5499</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7319</v>
+        <v>-0.3675</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1313</v>
+        <v>-1.1824</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3236</v>
+        <v>-1.2832</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3236</v>
+        <v>0.0408</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.3241</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5396</v>
+        <v>-0.2667</v>
       </c>
       <c r="N20" t="n">
         <v>-0.4083</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1313</v>
+        <v>0.1416</v>
       </c>
       <c r="P20" t="n">
         <v>0.1958</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3499</v>
+        <v>0.0518</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6228</v>
+        <v>0.1882</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2729</v>
+        <v>-0.1364</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BUENO DE LA ROSA</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7457</v>
+        <v>-1.3856</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.402</v>
+        <v>-0.9055</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3437</v>
+        <v>-0.4802</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5499</v>
+        <v>-1.8632</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3675</v>
+        <v>-1.7319</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1824</v>
+        <v>-0.1313</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2832</v>
+        <v>-1.3236</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0408</v>
+        <v>-1.3236</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3241</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2667</v>
+        <v>-0.5396</v>
       </c>
       <c r="N21" t="n">
         <v>-0.4083</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1416</v>
+        <v>-0.1313</v>
       </c>
       <c r="P21" t="n">
         <v>0.1958</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3917</v>
+        <v>0.2817</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1188</v>
+        <v>0.4182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2729</v>
+        <v>-0.1364</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4811</v>
+        <v>-1.4629</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3985</v>
+        <v>-1.0778</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8796</v>
+        <v>-0.3851</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3919</v>
+        <v>0.0319</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1698</v>
+        <v>-0.5587</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2221</v>
+        <v>0.5907</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7549</v>
+        <v>2.3829</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7145</v>
+        <v>1.9546</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0404</v>
+        <v>0.4283</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1468</v>
+        <v>-2.351</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8843</v>
+        <v>-2.5134</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2625</v>
+        <v>0.1624</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5875</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5875</v>
+        <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2435</v>
+        <v>-0.3785</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3564</v>
+        <v>-0.19</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1129</v>
+        <v>-0.1885</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4332</v>
+        <v>-0.3329</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6807</v>
+        <v>-2.1962</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9988</v>
+        <v>0.6032</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6819</v>
+        <v>-2.7994</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0319</v>
+        <v>-0.3919</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5587</v>
+        <v>-0.1698</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5907</v>
+        <v>-0.2221</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3829</v>
+        <v>0.7549</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9546</v>
+        <v>0.7145</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4283</v>
+        <v>0.0404</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.351</v>
+        <v>-1.1468</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.5134</v>
+        <v>-0.8843</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1624</v>
+        <v>-0.2625</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5963</v>
+        <v>0.0413</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.111</v>
+        <v>-0.1517</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4853</v>
+        <v>0.1931</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3329</v>
+        <v>-2.4332</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3787</v>
+        <v>-3.8579</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6772</v>
+        <v>-4.3702</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2985</v>
+        <v>0.5123</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6006</v>
@@ -2326,13 +2326,13 @@
         <v>2.546</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0743</v>
+        <v>-0.5534</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5652</v>
+        <v>-0.2582</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5091</v>
+        <v>-0.2952</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3329</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.816099999999999</v>
+        <v>-8.133900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6064</v>
+        <v>-3.606399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2098</v>
+        <v>-4.5277</v>
       </c>
       <c r="G25" t="n">
         <v>-7.1299</v>
@@ -2395,7 +2395,7 @@
         <v>2.2024</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9792000000000004</v>
+        <v>-0.9792000000000003</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.6264</v>
@@ -2404,13 +2404,13 @@
         <v>16.6469</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1763999999999999</v>
+        <v>0.8587000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.532100000000001</v>
+        <v>1.5323</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3556</v>
+        <v>-0.6732</v>
       </c>
       <c r="V25" t="n">
         <v>-0.8835999999999995</v>
